--- a/output/pdf_financials_xlsx/LEAP.xlsx
+++ b/output/pdf_financials_xlsx/LEAP.xlsx
@@ -5927,10 +5927,10 @@
         <v>1.210038</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>1.244784</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>1.673913</v>
       </c>
     </row>
     <row r="93">
@@ -10247,7 +10247,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/LEAP.xlsx
+++ b/output/pdf_financials_xlsx/LEAP.xlsx
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.004074</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.001444</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -2003,10 +2003,10 @@
         <v>-0.491495</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.550665</v>
+        <v>-0.554739</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.306452</v>
+        <v>-1.307896</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-1.524316</v>
@@ -2119,10 +2119,10 @@
         <v>-0.491495</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.550665</v>
+        <v>-0.554739</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.306452</v>
+        <v>-1.307896</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-1.524316</v>
@@ -2432,43 +2432,43 @@
         <v>0.309744</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.053946</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.044771</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.010696</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.504912</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.805281</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.456411</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.324854</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.476434</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.289881</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.197863</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.615599</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.11776</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>1.288467</v>
       </c>
     </row>
     <row r="35">
@@ -2548,43 +2548,43 @@
         <v>0.327744</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.053946</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.01575</v>
+        <v>0.060521</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.010696</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.504912</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.6525</v>
+        <v>1.457781</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.576</v>
+        <v>1.032411</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.324854</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.476434</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.289881</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.197863</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.615599</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.11776</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>1.288467</v>
       </c>
     </row>
     <row r="37">
@@ -3244,43 +3244,43 @@
         <v>0.008658000000000001</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.053946</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.044771</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.010696</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.504912</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.805281</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.456411</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.324854</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.476434</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.289881</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.197863</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.615599</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.140563</v>
+        <v>0.022803</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>1.367303</v>
+        <v>0.078836</v>
       </c>
     </row>
     <row r="49">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -39964,7 +39964,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">

--- a/output/pdf_financials_xlsx/LEAP.xlsx
+++ b/output/pdf_financials_xlsx/LEAP.xlsx
@@ -745,10 +745,10 @@
         <v>0.038914</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.045565</v>
+        <v>0.055982</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.033605</v>
+        <v>0.043605</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0.035549</v>
@@ -757,37 +757,37 @@
         <v>0.037566</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.028478</v>
+        <v>0.034478</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.05109</v>
+        <v>0.05809</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.049379</v>
+        <v>0.061379</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.105829</v>
+        <v>0.121829</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.07628699999999999</v>
+        <v>0.096287</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.094108</v>
+        <v>0.114108</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.09844700000000001</v>
+        <v>0.117447</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.060958</v>
+        <v>0.076958</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.07822999999999999</v>
+        <v>0.09422999999999999</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.046332</v>
+        <v>0.062332</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.084984</v>
+        <v>0.098984</v>
       </c>
     </row>
     <row r="8">
@@ -919,10 +919,10 @@
         <v>0.038914</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.045565</v>
+        <v>0.055982</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.033605</v>
+        <v>0.043605</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0.035549</v>
@@ -931,28 +931,28 @@
         <v>0.037566</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.028478</v>
+        <v>0.034478</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.05109</v>
+        <v>0.05809</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.049379</v>
+        <v>0.061379</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.105829</v>
+        <v>0.121829</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.07628699999999999</v>
+        <v>0.096287</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.094108</v>
+        <v>0.114108</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.09844700000000001</v>
+        <v>0.117447</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.060958</v>
+        <v>0.076958</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.316242</v>
@@ -1325,13 +1325,13 @@
         <v>0.137349</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.050721</v>
+        <v>-0.050721</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.027548</v>
+        <v>-0.027548</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.041731</v>
+        <v>-0.041731</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-0</v>
@@ -21374,7 +21374,11 @@
           <t>Shares issued for flow-through private placement 6,064,705 509,435 6,065</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -26146,7 +26150,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -28346,7 +28354,11 @@
           <t>Directors' fees (Note 7)</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -30512,7 +30524,11 @@
           <t>Directors' fees (Note 7)</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -32911,7 +32927,11 @@
           <t>Directors' Fees (Note 8)</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -39366,7 +39386,11 @@
           <t>Deferred Income Tax Recovery (Note 12)</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
@@ -41564,7 +41588,11 @@
           <t>Deferred Income Tax Recovery (note 12)</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E337" t="inlineStr">
         <is>
           <t>-</t>
